--- a/dataset/exports/kyzz-2010-2024-chapter.xlsx
+++ b/dataset/exports/kyzz-2010-2024-chapter.xlsx
@@ -133,7 +133,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第八章 共产主义崇高理想及其最终实现,考点2：共产主义社会的基本特征</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题八：共产主义论,考点2：共产主义社会的基本特征</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -210,7 +210,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第二章 唯物辩证法,考点3 量变质变规律（唯物辩证法第二规律）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点3 量变质变规律（唯物辩证法第二规律）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -287,7 +287,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点8：科学社会主义基本原则及其主要内容</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点8：科学社会主义基本原则及其主要内容</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -364,7 +364,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点8：劳动力成为商品与货币转化为资本</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点8：劳动力成为商品与货币转化为资本</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 社会主义改造理论</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第10章 建设社会主义文化强国</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2111</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点2 十月革命对中国的影响</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点2 十月革命对中国的影响</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第八章中华人民共和国的成立与中国社会主义建设道路的探索,考点11：《论十大关系》的发表</t>
+          <t xml:space="preserve">中国近现代史纲要,第八章 中华人民共和国的成立与中国社会主义建设道路的探索,考点11：《论十大关系》的发表</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点2 道德的功能与作用</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点2 道德的功能与作用</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点8 恪守职业道德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点8 恪守职业道德</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第15章 坚持“一国两制”和推进祖国完全统一</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点12 物质与意识的辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点12 物质与意识的辩证关系</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点11 科学技术在社会发展中的作用（第五动力）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点11 科学技术在社会发展中的作用（第五动力）</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点16：资本主义的国家,民主制度及其本质</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点16：资本主义的国家,民主制度及其本质</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第八章中华人民共和国的成立与中国社会主义建设道路的探索,考点4 过渡时期总路线的提出</t>
+          <t xml:space="preserve">中国近现代史纲要,第八章 中华人民共和国的成立与中国社会主义建设道路的探索,考点4 过渡时期总路线的提出</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点4 洋务运动的历史作用及其失败原因</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点4 洋务运动的历史作用及其失败原因</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点6：第二条战线的形成和发展</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点6：第二条战线的形成和发展</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第三章 弘扬中国精神,考点2 中国精神的丰富内涵</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第三章 继承优良传统 弘扬中国精神,考点2 中国精神的丰富内涵</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点13 我国宪法法律规定的权利</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点13 我国宪法法律规定的权利</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第16章 中国特色大国外交和推动构建人类命运共同体</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第二章 唯物辩证法,考点3 量变质变规律（唯物辩证法第二规律）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点3 量变质变规律（唯物辩证法第二规律）</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点5：私有制基础上商品经济的基本矛盾</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点5：私有制基础上商品经济的基本矛盾</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点5：社会主义在苏联一国的实践</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点5：社会主义在苏联一国的实践</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 “三个代表”重要思想,考点4：“三个代表”重要思想的主要内容</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第七章 “三个代表”重要思想,考点4：“三个代表”重要思想的主要内容</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十章 建设社会主义文化强国,考点1：文化是民族生存和发展的重要力量</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第10章 建设社会主义文化强国,考点1：文化是民族生存和发展的重要力量</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015</t>
+          <t xml:space="preserve">2111</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点12：反侵略战争的失败及原因</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点12：反侵略战争的失败及原因</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 中华民族的抗日战争</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 辛亥革命与君主专制制度的终结</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 中华民族的抗日战争</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第八章 科学发展观</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题六：资本主义论（下）</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1007</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -5985,7 +5985,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第五章 遵守道德规范 锤炼道德品格</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4005</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 领悟人生真谛 把握人生方向</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4001</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第八章 中华人民共和国的成立与中国社会主义建设道路的探索</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第八章 科学发展观</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第八章 科学发展观</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 进入近代后中华民族的磨难与抗争</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 进入近代后中华民族的磨难与抗争</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 中华民族的抗日战争</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第四章 中国共产党成立和中国革命新局面</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第10章 建设社会主义文化强国</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2111</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第11章 以保障和改善民生为重点加强社会建设</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 领悟人生真谛 把握人生方向</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4001</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9193,7 +9193,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题四：唯物史观</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1005</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -9297,7 +9297,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9347,7 +9347,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第八章 科学发展观</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第12章 建设社会主义生态文明</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 辛亥革命与君主专制制度的终结</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 中华民族的抗日战争</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -10298,7 +10298,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点2 实践的基本结构和形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点2 实践的基本结构和形式</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点13 主观能动性和客观规律性的辩证统一</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点13 主观能动性和客观规律性的辩证统一</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -10425,7 +10425,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点12：资本的循环周转与再生产</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点12：资本的循环周转与再生产</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点5：当代资本主义新变化的原因和实质</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点5：当代资本主义新变化的原因和实质</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点2：邓小平理论的形成过程</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点2：邓小平理论的形成过程</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O138" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点4：邓小平理论的主要内容</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点4：邓小平理论的主要内容</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10810,7 +10810,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第七章 “三个代表”重要思想</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2008</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点1 新文化运动与思想解放的潮流</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点1 新文化运动与思想解放的潮流</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点9 实行国共合作和掀起大革命高潮</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点9 实行国共合作和掀起大革命高潮</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第五章 中国革命的新道路</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第五章 遵守道德规范 锤炼道德品格</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4005</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点11 物质运动和时空</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点11 物质运动和时空</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点14 个人在社会历史中的作用</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点14 个人在社会历史中的作用</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点3：价值如何表现</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点3：价值如何表现</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点4：当代资本主义经济政治新变化的表现和特点</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点4：当代资本主义经济政治新变化的表现和特点</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点5：社会主义在苏联一国的实践</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点5：社会主义在苏联一国的实践</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -11915,7 +11915,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第12章 建设社会主义生态文明</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第七章 科学发展观,考点3：科学发展观的科学内涵</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第八章 科学发展观,考点3：科学发展观的科学内涵</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">3003</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点2：中国共产党争取民主和平的斗争</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点2：中国共产党争取民主和平的斗争</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第三章 弘扬中国精神,考点2 中国精神的丰富内涵</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第三章 继承优良传统 弘扬中国精神,考点2 中国精神的丰富内涵</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点3 实践对认识的决定作用</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点3 实践对认识的决定作用</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点11：资本的积累</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点11：资本的积累</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -13071,7 +13071,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成,考点3：走中国工业化道路的思想</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成果,考点3：走中国工业化道路的思想</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点2：邓小平理论的形成过程</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点2：邓小平理论的形成过程</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第11章 以保障和改善民生为重点加强社会建设</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十五章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第15章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点5：近代中国的主要矛盾和历史任务</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点5：近代中国的主要矛盾和历史任务</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3003</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点2 十月革命对中国的影响</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点2 十月革命对中国的影响</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
@@ -13764,7 +13764,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第一章 人生的青春之问,考点7 人生价值的评价与实现</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第一章 领悟人生真谛 把握人生方向,考点7 人生价值的评价与实现</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -13918,7 +13918,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十三章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第13章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
@@ -13995,7 +13995,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点11 物质运动和时空</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点11 物质运动和时空</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第二章 唯物辩证法,考点4 否定之否定规律（唯物辩证法第三规律）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点4 否定之否定规律（唯物辩证法第三规律）</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点14 个人在社会历史中的作用</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点14 个人在社会历史中的作用</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -14303,7 +14303,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点15：资本主义的基本矛盾与经济危机</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点15：资本主义的基本矛盾与经济危机</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点2：垄断资本主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点2：垄断资本主义的发展</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第七章 社会主义现代化建设的教育,科技,人才战略,考点4：加快建设人才强国</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第7章 社会主义现代化建设的教育,科技,人才战略,考点4：加快建设人才强国</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012</t>
+          <t xml:space="preserve">2108</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第九章 改革开放与中国特色社会主义的开创和发展</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第八章 发展全过程人民民主,考点3：健全人民当家作主的制度体系</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第8章 发展全过程人民民主,考点3：健全人民当家作主的制度体系</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
@@ -14765,7 +14765,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第四章 践行社会主义核心价值观,考点2 当代中国发展进步的精神指引</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第四章 明确价值要求 践行价值准则,考点2 当代中国发展进步的精神指引</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点11：义和团运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点11：义和团运动</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第七章 为建立新中国而奋斗</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第九章中国特色社会主义的开创与接续发展,考点5：科学评价毛泽东和毛泽东思想</t>
+          <t xml:space="preserve">中国近现代史纲要,第九章 改革开放与中国特色社会主义的开创和发展,考点5：科学评价毛泽东和毛泽东思想</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3009</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点10 锤炼个人品德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点10 锤炼个人品德</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点12 法律权利与法律义务</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点12 法律权利与法律义务</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 中华民族的抗日战争</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
@@ -15304,7 +15304,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
@@ -15381,7 +15381,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第二章 唯物辩证法,考点3 量变质变规律（唯物辩证法第二规律）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点3 量变质变规律（唯物辩证法第二规律）</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点15 从必然走向自由</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点15 从必然走向自由</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点10：剩余价值的生产</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点10：剩余价值的生产</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -15612,7 +15612,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点2：垄断资本主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点2：垄断资本主义的发展</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -15689,7 +15689,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成,考点1：调动一切积极因素为社会主义事业服务</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成果,考点1：调动一切积极因素为社会主义事业服务</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -15997,7 +15997,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点13：民族意识的觉醒</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点13：民族意识的觉醒</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点13：民族意识的觉醒</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点13：民族意识的觉醒</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -16201,7 +16201,7 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点5：土地改革与农民的广泛发动</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点5：土地改革与农民的广泛发动</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
@@ -16305,7 +16305,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第三章 弘扬中国精神,考点3 实现中国梦必须弘扬中国精神</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第三章 继承优良传统 弘扬中国精神,考点3 实现中国梦必须弘扬中国精神</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点11 培养社会主义法治思想</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点11 培养社会主义法治思想</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点15 世界的物质统一性原理</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点15 世界的物质统一性原理</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点11 物质运动和时空</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点11 物质运动和时空</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -16767,7 +16767,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点15：资本主义的基本矛盾与经济危机</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点15：资本主义的基本矛盾与经济危机</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点3：经济全球化及其影响</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点3：经济全球化及其影响</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点1：空想社会主义的产生,发展和局限性</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点1：空想社会主义的产生,发展和局限性</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O223" t="inlineStr">
@@ -17229,7 +17229,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点6 戊戌维新运动的历史意义,失败原因和教训</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点6 戊戌维新运动的历史意义,失败原因和教训</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点1 新文化运动与思想解放的潮流</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点1 新文化运动与思想解放的潮流</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
@@ -17537,7 +17537,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第九章中国特色社会主义的开创与接续发展,考点10：邓小平南方谈话</t>
+          <t xml:space="preserve">中国近现代史纲要,第九章 改革开放与中国特色社会主义的开创和发展,考点10：邓小平南方谈话</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">3009</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O228" t="inlineStr">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点6 建设法治中国</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点6 建设法治中国</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点12 法律权利与法律义务</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点12 法律权利与法律义务</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O231" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O232" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点13 主观能动性和客观规律性的辩证统一</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点13 主观能动性和客观规律性的辩证统一</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点12 物质与意识的辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点12 物质与意识的辩证关系</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点13：工资与剩余价值的分配</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点13：工资与剩余价值的分配</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点4：当代资本主义经济政治新变化的表现和特点</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点4：当代资本主义经济政治新变化的表现和特点</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -18357,7 +18357,7 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -18434,7 +18434,7 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第九章 改革开放与中国特色社会主义的开创和发展</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点11：义和团运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点11：义和团运动</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点3 五四运动的发生和发展</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点3 五四运动的发生和发展</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O242" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="N243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="O243" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点4：全国解放战争的顺利发展</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点4：全国解放战争的顺利发展</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O244" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第二章 坚定理想信念,考点1 理想信念</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第二章 追求远大理想 坚定崇高信念,考点1 理想信念</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -18923,7 +18923,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第一章 人生的青春之问,考点7 人生价值的评价与实现</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第一章 领悟人生真谛 把握人生方向,考点7 人生价值的评价与实现</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -19000,7 +19000,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第15章 坚持“一国两制”和推进祖国完全统一</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O247" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点2 实践的基本结构和形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点2 实践的基本结构和形式</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -19231,7 +19231,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点14 个人在社会历史中的作用</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点14 个人在社会历史中的作用</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -19308,7 +19308,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点11：资本的积累</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点11：资本的积累</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -19385,7 +19385,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点11：资本的积累</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点11：资本的积累</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -19462,7 +19462,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点5：社会主义在苏联一国的实践</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点5：社会主义在苏联一国的实践</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第四章 中国共产党成立和中国革命新局面</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
@@ -19666,7 +19666,7 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
@@ -19693,7 +19693,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十二章 建设社会主义生态文明,考点1：坚持人与自然和谐共生</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第12章 建设社会主义生态文明,考点1：坚持人与自然和谐共生</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
@@ -19770,7 +19770,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
@@ -19847,7 +19847,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 毛泽东思想及其历史地位</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -19897,7 +19897,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
@@ -19924,7 +19924,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题五：资本主义论（上）</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1006</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3003</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第九章中国特色社会主义的开创与接续发展,考点2：中共十一届三中全会的伟大转折</t>
+          <t xml:space="preserve">中国近现代史纲要,第九章 改革开放与中国特色社会主义的开创和发展,考点2：中共十一届三中全会的伟大转折</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -20128,7 +20128,7 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3009</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点1 法律的含义</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点1 法律的含义</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点12 法律权利与法律义务</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点12 法律权利与法律义务</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
@@ -20463,7 +20463,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,导论,考点3 马克思主义的创立</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题一：马克思主义观,考点3 马克思主义的创立</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第二章 唯物辩证法,考点2 对立统一规律（唯物辩证法第一规律）</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点2 对立统一规律（唯物辩证法第一规律）</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点13 人民群众创造历史</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点13 人民群众创造历史</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -20694,7 +20694,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点1：价值是什么</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点1：价值是什么</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点4：邓小平理论的主要内容</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点4：邓小平理论的主要内容</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第七章 科学发展观,考点4：科学发展观的主要内容</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第八章 科学发展观,考点4：科学发展观的主要内容</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第七章 社会主义现代化建设的教育,科技,人才战略,考点1：全面建设社会主义现代化国家的基础性,战略性支撑</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第7章 社会主义现代化建设的教育,科技,人才战略,考点1：全面建设社会主义现代化国家的基础性,战略性支撑</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -20976,7 +20976,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012</t>
+          <t xml:space="preserve">2108</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十五章 坚持“一国两制”和推进祖国完全统一,考点3：推进祖国完全统一</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第15章 坚持“一国两制”和推进祖国完全统一,考点3：推进祖国完全统一</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -21053,7 +21053,7 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点5：近代中国的主要矛盾和历史任务</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点5：近代中国的主要矛盾和历史任务</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -21130,7 +21130,7 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -21157,7 +21157,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点3 洋务事业的兴办</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点3 洋务事业的兴办</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -21207,7 +21207,7 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点11：中国革命胜利的原因和经验</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点11：中国革命胜利的原因和经验</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -21284,7 +21284,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点7 遵守社会公德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点7 遵守社会公德</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点6 建设法治中国</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点6 建设法治中国</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -21542,7 +21542,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -21592,7 +21592,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O280" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第16章 中国特色大国外交和推动构建人类命运共同体</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -21669,7 +21669,7 @@
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
       <c r="O281" t="inlineStr">
@@ -21696,7 +21696,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点15 世界的物质统一性原理</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点15 世界的物质统一性原理</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点11：资本的积累</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点11：资本的积累</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -21928,7 +21928,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点4：当代资本主义经济政治新变化的表现和特点</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点4：当代资本主义经济政治新变化的表现和特点</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -22005,7 +22005,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点10：社会主义建设的曲折发展与不断完善</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点10：社会主义建设的曲折发展与不断完善</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
@@ -22159,7 +22159,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -22209,7 +22209,7 @@
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O288" t="inlineStr">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O289" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十七章 全面从严治党,考点2：以政治建设为统领深入推进党的建设</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第17章 全面从严治党,考点2：以政治建设为统领深入推进党的建设</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2118</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -22440,7 +22440,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
@@ -22594,7 +22594,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第八章中华人民共和国的成立与中国社会主义建设道路的探索,考点5 实行社会主义改造的必要性和条件</t>
+          <t xml:space="preserve">中国近现代史纲要,第八章 中华人民共和国的成立与中国社会主义建设道路的探索,考点5 实行社会主义改造的必要性和条件</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -22671,7 +22671,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -22698,7 +22698,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点3 我国社会主义法律的运行</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点3 我国社会主义法律的运行</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点5 坚持走中国特色社会主义法治道路</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点5 坚持走中国特色社会主义法治道路</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -22902,7 +22902,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -22979,7 +22979,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,导论,考点4 马克思主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题一：马克思主义观,考点4 马克思主义的发展</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -23056,7 +23056,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
@@ -23083,7 +23083,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点11 物质运动和时空</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点11 物质运动和时空</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -23133,7 +23133,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点5：私有制基础上商品经济的基本矛盾</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点5：私有制基础上商品经济的基本矛盾</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,导论,考点3 习近平新时代中国特色社会主义思想是完整的科学体系</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,习思：导论,考点3 习近平新时代中国特色社会主义思想是完整的科学体系</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -23364,7 +23364,7 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">2101</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十三章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第13章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十七章 全面从严治党,考点1：全面从严治党是新时代党的建设的鲜明主题</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第17章 全面从严治党,考点1：全面从严治党是新时代党的建设的鲜明主题</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -23518,7 +23518,7 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2118</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点4：建设现代化经济体系</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点4：建设现代化经济体系</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点6 戊戌维新运动的历史意义,失败原因和教训</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点6 戊戌维新运动的历史意义,失败原因和教训</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点8 制定革命纲领，发动工农运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点8 制定革命纲领，发动工农运动</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
@@ -23826,7 +23826,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点2：中国共产党争取民主和平的斗争</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点2：中国共产党争取民主和平的斗争</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第四章 践行社会主义核心价值观,考点6 扣好人生的扣子</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第四章 明确价值要求 践行价值准则,考点6 扣好人生的扣子</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第一章 人生的青春之问,考点3 人生观的主要内容</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第一章 领悟人生真谛 把握人生方向,考点3 人生观的主要内容</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第14章 建设巩固国防和强大人民军队</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2115</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
@@ -24238,7 +24238,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点2 实践的基本结构和形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点2 实践的基本结构和形式</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点12 真理与价值的辩证统一</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点12 真理与价值的辩证统一</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -24392,7 +24392,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点13：工资与剩余价值的分配</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点13：工资与剩余价值的分配</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -24469,7 +24469,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点9：社会主义代替资本主义是一个长期的历史过程</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点9：社会主义代替资本主义是一个长期的历史过程</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点8：科学社会主义基本原则及其主要内容</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点8：科学社会主义基本原则及其主要内容</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -24623,7 +24623,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第一章 新时代坚持和发展中国特色社会主义,考点2 中国特色社会主义进入新时代</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第1章 新时代坚持和发展中国特色社会主义,考点2 中国特色社会主义进入新时代</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002</t>
+          <t xml:space="preserve">2102</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -24700,7 +24700,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -24750,7 +24750,7 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O321" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第五章 全面深化改革开放,考点2：统筹推进各领域各方面改革开放</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第5章 全面深化改革开放,考点2：统筹推进各领域各方面改革开放</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O322" t="inlineStr">
@@ -24854,7 +24854,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十五章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第15章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -24904,7 +24904,7 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O323" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第一章 新时代坚持和发展中国特色社会主义,考点1 方向决定道路，道路决定命运</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第1章 新时代坚持和发展中国特色社会主义,考点1 方向决定道路，道路决定命运</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -24981,7 +24981,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002</t>
+          <t xml:space="preserve">2102</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第八章中华人民共和国的成立与中国社会主义建设道路的探索,考点1 中华人民共和国的成立及其伟大意义</t>
+          <t xml:space="preserve">中国近现代史纲要,第八章 中华人民共和国的成立与中国社会主义建设道路的探索,考点1 中华人民共和国的成立及其伟大意义</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第九章 改革开放与中国特色社会主义的开创和发展</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -25212,7 +25212,7 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
@@ -25239,7 +25239,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第四章 践行社会主义核心价值观,考点2 当代中国发展进步的精神指引</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第四章 明确价值要求 践行价值准则,考点2 当代中国发展进步的精神指引</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点5 坚持走中国特色社会主义法治道路</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点5 坚持走中国特色社会主义法治道路</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -25443,7 +25443,7 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
@@ -25470,7 +25470,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第15章 坚持“一国两制”和推进祖国完全统一</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -25520,7 +25520,7 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
@@ -25547,7 +25547,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,导论,考点4 马克思主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题一：马克思主义观,考点4 马克思主义的发展</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -25597,7 +25597,7 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点12 真理与价值的辩证统一</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点12 真理与价值的辩证统一</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -25701,7 +25701,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点2：价值如何衡量</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点2：价值如何衡量</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点5：社会主义在苏联一国的实践</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点5：社会主义在苏联一国的实践</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -25855,7 +25855,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点3：邓小平理论回答的基本问题</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点3：邓小平理论回答的基本问题</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -25905,7 +25905,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -26009,7 +26009,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第七章 为建立新中国而奋斗</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十五章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第15章 坚持“一国两制”和推进祖国完全统一,考点1：全面准确理解和贯彻“一国两制”方针</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -26136,7 +26136,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019</t>
+          <t xml:space="preserve">2116</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点5：近代中国的主要矛盾和历史任务</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点5：近代中国的主要矛盾和历史任务</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">3003</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
@@ -26317,7 +26317,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点8 制定革命纲领，发动工农运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点8 制定革命纲领，发动工农运动</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -26367,7 +26367,7 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
@@ -26445,7 +26445,7 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点6 建设法治中国</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点6 建设法治中国</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第三章 弘扬中国精神,考点4 新时代的爱国主义</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第三章 继承优良传统 弘扬中国精神,考点4 新时代的爱国主义</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -26676,7 +26676,7 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -26753,7 +26753,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点11 物质运动和时空</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点11 物质运动和时空</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -26830,7 +26830,7 @@
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
@@ -26857,7 +26857,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -27011,7 +27011,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点12：资本的循环周转与再生产</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点12：资本的循环周转与再生产</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点2：垄断资本主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点2：垄断资本主义的发展</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第一章 新时代坚持和发展中国特色社会主义,考点2 中国特色社会主义进入新时代</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第1章 新时代坚持和发展中国特色社会主义,考点2 中国特色社会主义进入新时代</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002</t>
+          <t xml:space="preserve">2102</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
@@ -27242,7 +27242,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -27292,7 +27292,7 @@
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
@@ -27319,7 +27319,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第二章 以中国式现代化全面推进中华民族伟大复兴,考点1：中华民族近代以来最伟大的梦想</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第2章 以中国式现代化全面推进中华民族伟大复兴,考点1：中华民族近代以来最伟大的梦想</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
@@ -27396,7 +27396,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十二章 建设社会主义生态文明,考点2：建设美丽中国</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第12章 建设社会主义生态文明,考点2：建设美丽中国</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
@@ -27473,7 +27473,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第八章 发展全过程人民民主,考点4：巩固和发展新时代爱国统一战线</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第8章 发展全过程人民民主,考点4：巩固和发展新时代爱国统一战线</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
@@ -27550,7 +27550,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点4：近代中国社会的半殖民地半封建性质</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点4：近代中国社会的半殖民地半封建性质</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
@@ -27627,7 +27627,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点5 中国早期马克思主义思想运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点5 中国早期马克思主义思想运动</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
@@ -27704,7 +27704,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第八章中华人民共和国的成立与中国社会主义建设道路的探索,考点2 巩固新政权的伟大斗争</t>
+          <t xml:space="preserve">中国近现代史纲要,第八章 中华人民共和国的成立与中国社会主义建设道路的探索,考点2 巩固新政权的伟大斗争</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="N360" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">3009</t>
         </is>
       </c>
       <c r="O360" t="inlineStr">
@@ -27781,7 +27781,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点4 传承中华传统美德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点4 传承中华传统美德</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -27858,7 +27858,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点14 依法行使法律权利</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点14 依法行使法律权利</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -27985,7 +27985,7 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O363" t="inlineStr">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O364" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,导论,考点4 马克思主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题一：马克思主义观,考点4 马克思主义的发展</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O365" t="inlineStr">
@@ -28166,7 +28166,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点1 唯物史观和唯心史观的对立</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点1 唯物史观和唯心史观的对立</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -28320,7 +28320,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -28370,7 +28370,7 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O368" t="inlineStr">
@@ -28447,7 +28447,7 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O369" t="inlineStr">
@@ -28474,7 +28474,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点3：加快构建新发展格局</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点3：加快构建新发展格局</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -28524,7 +28524,7 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O370" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点4：邓小平理论的主要内容</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点4：邓小平理论的主要内容</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -28601,7 +28601,7 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O371" t="inlineStr">
@@ -28628,7 +28628,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点1：完整,准确,全面贯彻新发展理念</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -28678,7 +28678,7 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O372" t="inlineStr">
@@ -28705,7 +28705,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点3 洋务事业的兴办</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点3 洋务事业的兴办</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O373" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O374" t="inlineStr">
@@ -28859,7 +28859,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点10：中国人民政协与《共同纲领》</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点10：中国人民政协与《共同纲领》</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -28909,7 +28909,7 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O375" t="inlineStr">
@@ -28986,7 +28986,7 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
       <c r="O376" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第二章 坚定理想信念,考点8 个人理想与社会理想的统一</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第二章 追求远大理想 坚定崇高信念,考点8 个人理想与社会理想的统一</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第三章 弘扬中国精神,考点4 新时代的爱国主义</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第三章 继承优良传统 弘扬中国精神,考点4 新时代的爱国主义</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -29217,7 +29217,7 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O379" t="inlineStr">
@@ -29294,7 +29294,7 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O380" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点9 物质和运动</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点9 物质和运动</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -29371,7 +29371,7 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O381" t="inlineStr">
@@ -29398,7 +29398,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点3 生产力和生产关系矛盾运动的规律</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点3 生产力和生产关系矛盾运动的规律</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -29475,7 +29475,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点1：价值是什么</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点1：价值是什么</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点11：资本的积累</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点11：资本的积累</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点3：第一国际和巴黎公社</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点3：第一国际和巴黎公社</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -29706,7 +29706,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第四章 社会主义建设道路初步探索的理论成果</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -29756,7 +29756,7 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
       <c r="O386" t="inlineStr">
@@ -29783,7 +29783,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第七章 社会主义现代化建设的教育,科技,人才战略,考点1：全面建设社会主义现代化国家的基础性,战略性支撑</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第7章 社会主义现代化建设的教育,科技,人才战略,考点1：全面建设社会主义现代化国家的基础性,战略性支撑</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012</t>
+          <t xml:space="preserve">2108</t>
         </is>
       </c>
       <c r="O387" t="inlineStr">
@@ -29861,7 +29861,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -29911,7 +29911,7 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O388" t="inlineStr">
@@ -29938,7 +29938,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第11章 以保障和改善民生为重点加强社会建设</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -29988,7 +29988,7 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="O389" t="inlineStr">
@@ -30015,7 +30015,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第八章 发展全过程人民民主,考点4：巩固和发展新时代爱国统一战线</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第8章 发展全过程人民民主,考点4：巩固和发展新时代爱国统一战线</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
       <c r="O390" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点3：鸦片战争的爆发</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点3：鸦片战争的爆发</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -30142,7 +30142,7 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O391" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第四章中国共产党成立和中国革命新局面,考点5 中国早期马克思主义思想运动</t>
+          <t xml:space="preserve">中国近现代史纲要,第四章 中国共产党成立和中国革命新局面,考点5 中国早期马克思主义思想运动</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -30219,7 +30219,7 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t xml:space="preserve">3004</t>
+          <t xml:space="preserve">3005</t>
         </is>
       </c>
       <c r="O392" t="inlineStr">
@@ -30246,7 +30246,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成,考点4：初步探索的意义和经验教训</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成果,考点4：初步探索的意义和经验教训</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -30296,7 +30296,7 @@
       </c>
       <c r="N393" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
       <c r="O393" t="inlineStr">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点5 坚持走中国特色社会主义法治道路</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点5 坚持走中国特色社会主义法治道路</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -30400,7 +30400,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点16 不断提升法治素养</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点16 不断提升法治素养</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -30477,7 +30477,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第13章 维护和塑造国家安全</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -30527,7 +30527,7 @@
       </c>
       <c r="N396" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
       <c r="O396" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="N397" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O397" t="inlineStr">
@@ -30631,7 +30631,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,导论,考点5 马克思主义的鲜明特征</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题一：马克思主义观,考点5 马克思主义的鲜明特征</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -30681,7 +30681,7 @@
       </c>
       <c r="N398" t="inlineStr">
         <is>
-          <t xml:space="preserve">1001</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O398" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点3 生产力和生产关系矛盾运动的规律</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点3 生产力和生产关系矛盾运动的规律</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -30785,7 +30785,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点3：价值如何表现</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点3：价值如何表现</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点4：当代资本主义经济政治新变化的表现和特点</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点4：当代资本主义经济政治新变化的表现和特点</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -30939,7 +30939,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 邓小平理论</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -30989,7 +30989,7 @@
       </c>
       <c r="N402" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O402" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点3：加快构建新发展格局</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点3：加快构建新发展格局</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -31066,7 +31066,7 @@
       </c>
       <c r="N403" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O403" t="inlineStr">
@@ -31093,7 +31093,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点4：建设现代化经济体系</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点4：建设现代化经济体系</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -31143,7 +31143,7 @@
       </c>
       <c r="N404" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O404" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十章 建设社会主义文化强国,考点4：铸就社会主义文化新辉煌</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第10章 建设社会主义文化强国,考点4：铸就社会主义文化新辉煌</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015</t>
+          <t xml:space="preserve">2111</t>
         </is>
       </c>
       <c r="O405" t="inlineStr">
@@ -31247,7 +31247,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第二章 对国家出路的早期探索,考点5 戊戌维新运动的开展</t>
+          <t xml:space="preserve">中国近现代史纲要,第二章 不同社会力量对国家出路的早期探索,考点5 戊戌维新运动的开展</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">3003</t>
         </is>
       </c>
       <c r="O406" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O407" t="inlineStr">
@@ -31401,7 +31401,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第七章 为新中国而奋斗,考点10：中国人民政协与《共同纲领》</t>
+          <t xml:space="preserve">中国近现代史纲要,第七章 为建立新中国而奋斗,考点10：中国人民政协与《共同纲领》</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -31451,7 +31451,7 @@
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O408" t="inlineStr">
@@ -31478,7 +31478,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成,考点1：调动一切积极因素为社会主义事业服务</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第四章 社会主义建设道路初步探索的理论成果,考点1：调动一切积极因素为社会主义事业服务</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -31528,7 +31528,7 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">2005</t>
         </is>
       </c>
       <c r="O409" t="inlineStr">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点4 传承中华传统美德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点4 传承中华传统美德</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -31632,7 +31632,7 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点2 社会存在和社会意识及其辩证关系</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O412" t="inlineStr">
@@ -31836,7 +31836,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O413" t="inlineStr">
@@ -31863,7 +31863,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点15 世界的物质统一性原理</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点15 世界的物质统一性原理</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -31913,7 +31913,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O414" t="inlineStr">
@@ -31940,7 +31940,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点8 物质范畴及其理论意义</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点8 物质范畴及其理论意义</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -31990,7 +31990,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O415" t="inlineStr">
@@ -32017,7 +32017,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第一章 辩证唯物论,考点9 物质和运动</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题二：辩证唯物主义世界观,考点9 物质和运动</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -32067,7 +32067,7 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O416" t="inlineStr">
@@ -32094,7 +32094,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点1 唯物史观和唯心史观的对立</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点1 唯物史观和唯心史观的对立</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点7：资本主义的历史地位</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点7：资本主义的历史地位</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -32248,7 +32248,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点4：建设现代化经济体系</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点4：建设现代化经济体系</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -32298,7 +32298,7 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O419" t="inlineStr">
@@ -32375,7 +32375,7 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O420" t="inlineStr">
@@ -32402,7 +32402,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第八章 发展全过程人民民主,考点2：全过程人民民主是社会主义民主政治的本质属性</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第8章 发展全过程人民民主,考点2：全过程人民民主是社会主义民主政治的本质属性</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
       <c r="O421" t="inlineStr">
@@ -32479,7 +32479,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十二章 建设社会主义生态文明,考点2：建设美丽中国</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第12章 建设社会主义生态文明,考点2：建设美丽中国</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -32529,7 +32529,7 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O422" t="inlineStr">
@@ -32556,7 +32556,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十六章 中国特色大国外交和推动构建人类命运共同体,考点3：推动构建人类命运共同体</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第16章 中国特色大国外交和推动构建人类命运共同体,考点3：推动构建人类命运共同体</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -32606,7 +32606,7 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
       <c r="O423" t="inlineStr">
@@ -32683,7 +32683,7 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O424" t="inlineStr">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O425" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第5章 全面深化改革开放</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -32837,7 +32837,7 @@
       </c>
       <c r="N426" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="O426" t="inlineStr">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第五章 遵守道德规范 锤炼道德品格</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="N427" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4005</t>
         </is>
       </c>
       <c r="O427" t="inlineStr">
@@ -32941,7 +32941,7 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点4 全面依法治国的根本遵循</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点4 全面依法治国的根本遵循</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
@@ -33068,7 +33068,7 @@
       </c>
       <c r="N429" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O429" t="inlineStr">
@@ -33145,7 +33145,7 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O430" t="inlineStr">
@@ -33172,7 +33172,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -33222,7 +33222,7 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O431" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点6 社会形态更替的一般规律及特殊形式</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -33326,7 +33326,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点2：价值如何衡量</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点2：价值如何衡量</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -33403,7 +33403,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点1：资本主义从自由竞争到垄断</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点1：资本主义从自由竞争到垄断</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -33481,7 +33481,7 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第五章 邓小平理论,考点3：邓小平理论回答的基本问题</t>
+          <t xml:space="preserve">毛泽东思想和中国特色社会主义,第六章 邓小平理论,考点3：邓小平理论回答的基本问题</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -33531,7 +33531,7 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">2007</t>
         </is>
       </c>
       <c r="O435" t="inlineStr">
@@ -33558,7 +33558,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十一章：以改善和保障民生为重点加强社会建设,考点2：不断提高人民生活品质</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第11章 以保障和改善民生为重点加强社会建设,考点2：不断提高人民生活品质</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -33608,7 +33608,7 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="O436" t="inlineStr">
@@ -33635,7 +33635,7 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十三章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第13章 维护和塑造国家安全,考点1：坚持总体国家安全观</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -33685,7 +33685,7 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018</t>
+          <t xml:space="preserve">2114</t>
         </is>
       </c>
       <c r="O437" t="inlineStr">
@@ -33712,7 +33712,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十七章 全面从严治党,考点4：建设长期执政的马克思主义政党</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第17章 全面从严治党,考点4：建设长期执政的马克思主义政党</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -33762,7 +33762,7 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021</t>
+          <t xml:space="preserve">2118</t>
         </is>
       </c>
       <c r="O438" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第一章 反对外国侵略的斗争,考点1：中国封建社会的衰落</t>
+          <t xml:space="preserve">中国近现代史纲要,第一章 进入近代后中华民族的磨难与抗争,考点1：中国封建社会的衰落</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -33839,7 +33839,7 @@
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O439" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O440" t="inlineStr">
@@ -33993,7 +33993,7 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">3007</t>
         </is>
       </c>
       <c r="O441" t="inlineStr">
@@ -34070,7 +34070,7 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006</t>
+          <t xml:space="preserve">2004</t>
         </is>
       </c>
       <c r="O442" t="inlineStr">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点7 遵守社会公德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点7 遵守社会公德</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点4 全面依法治国的根本遵循</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点4 全面依法治国的根本遵循</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -34301,7 +34301,7 @@
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O445" t="inlineStr">
@@ -34328,7 +34328,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第16章 中国特色大国外交和推动构建人类命运共同体</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -34378,7 +34378,7 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2117</t>
         </is>
       </c>
       <c r="O446" t="inlineStr">
@@ -34405,7 +34405,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第四章 唯物史观,考点14 个人在社会历史中的作用</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题四：唯物史观,考点14 个人在社会历史中的作用</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
@@ -34482,7 +34482,7 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第三章 认识论,考点12 真理与价值的辩证统一</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题三：辩证唯物主义认识论,考点12 真理与价值的辩证统一</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -34559,7 +34559,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第五章 资本主义的本质及规律,考点13：工资与剩余价值的分配</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题五：资本主义论（上）,考点13：工资与剩余价值的分配</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
@@ -34636,7 +34636,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第六章 资本主义的发展及趋势,考点2：垄断资本主义的发展</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题六：资本主义论（下）,考点2：垄断资本主义的发展</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t xml:space="preserve">马克思主义基本原理概论,第七章 社会主义社会的发展及其规律,考点5：社会主义在苏联一国的实践</t>
+          <t xml:space="preserve">马克思主义基本原理概论,专题七：社会主义论,考点5：社会主义在苏联一国的实践</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -34840,7 +34840,7 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">2002</t>
         </is>
       </c>
       <c r="O452" t="inlineStr">
@@ -34867,7 +34867,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第六章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第6章 推动高质量发展,考点2：坚持和完善社会主义基本经济制度</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -34917,7 +34917,7 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O453" t="inlineStr">
@@ -34994,7 +34994,7 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O454" t="inlineStr">
@@ -35021,7 +35021,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t xml:space="preserve">新时代中国特色社会主义思想概论,第十二章 建设社会主义生态文明,考点1：坚持人与自然和谐共生</t>
+          <t xml:space="preserve">新时代中国特色社会主义思想概论,第12章 建设社会主义生态文明,考点1：坚持人与自然和谐共生</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -35071,7 +35071,7 @@
       </c>
       <c r="N455" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">2113</t>
         </is>
       </c>
       <c r="O455" t="inlineStr">
@@ -35098,7 +35098,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点4 传承中华传统美德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点4 传承中华传统美德</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -35225,7 +35225,7 @@
       </c>
       <c r="N457" t="inlineStr">
         <is>
-          <t xml:space="preserve">3003</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O457" t="inlineStr">
@@ -35302,7 +35302,7 @@
       </c>
       <c r="N458" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="O458" t="inlineStr">
@@ -35329,7 +35329,7 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t xml:space="preserve">中国近现代史纲要,第九章中国特色社会主义的开创与接续发展,考点2：中共十一届三中全会的伟大转折</t>
+          <t xml:space="preserve">中国近现代史纲要,第九章 改革开放与中国特色社会主义的开创和发展,考点2：中共十一届三中全会的伟大转折</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -35379,7 +35379,7 @@
       </c>
       <c r="N459" t="inlineStr">
         <is>
-          <t xml:space="preserve">3009</t>
+          <t xml:space="preserve">3010</t>
         </is>
       </c>
       <c r="O459" t="inlineStr">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第五章 明大德守公德严私德,考点3 社会主义道德是崭新类型的道德</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第五章 遵守道德规范 锤炼道德品格,考点3 社会主义道德是崭新类型的道德</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -35483,7 +35483,7 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t xml:space="preserve">思想道德修养与法律基础,第六章 遵法学法守法用法,考点12 法律权利与法律义务</t>
+          <t xml:space="preserve">思想道德修养与法律基础,第六章 学习法治思想 提升法治素养,考点12 法律权利与法律义务</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="N462" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O462" t="inlineStr">
@@ -35687,7 +35687,7 @@
       </c>
       <c r="N463" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O463" t="inlineStr">
@@ -35714,7 +35714,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -35764,7 +35764,7 @@
       </c>
       <c r="N464" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O464" t="inlineStr">
@@ -35791,7 +35791,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -35841,7 +35841,7 @@
       </c>
       <c r="N465" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O465" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -35918,7 +35918,7 @@
       </c>
       <c r="N466" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O466" t="inlineStr">
@@ -35945,7 +35945,7 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
@@ -35995,7 +35995,7 @@
       </c>
       <c r="N467" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O467" t="inlineStr">
@@ -36022,7 +36022,7 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -36072,7 +36072,7 @@
       </c>
       <c r="N468" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O468" t="inlineStr">
@@ -36099,7 +36099,7 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第1章 新时代坚持和发展中国特色社会主义</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -36149,7 +36149,7 @@
       </c>
       <c r="N469" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2102</t>
         </is>
       </c>
       <c r="O469" t="inlineStr">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第11章 以保障和改善民生为重点加强社会建设</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -36226,7 +36226,7 @@
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
@@ -36303,7 +36303,7 @@
       </c>
       <c r="N471" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O471" t="inlineStr">
@@ -36330,7 +36330,7 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
@@ -36380,7 +36380,7 @@
       </c>
       <c r="N472" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O472" t="inlineStr">
@@ -36407,7 +36407,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 进入近代后中华民族的磨难与抗争</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -36457,7 +36457,7 @@
       </c>
       <c r="N473" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3002</t>
         </is>
       </c>
       <c r="O473" t="inlineStr">
@@ -36484,7 +36484,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 继承优良传统 弘扬中国精神</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="N474" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4003</t>
         </is>
       </c>
       <c r="O474" t="inlineStr">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题六：资本主义论（下）</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -36611,7 +36611,7 @@
       </c>
       <c r="N475" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1007</t>
         </is>
       </c>
       <c r="O475" t="inlineStr">
@@ -36638,7 +36638,7 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第七章 为建立新中国而奋斗</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -36688,7 +36688,7 @@
       </c>
       <c r="N476" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3008</t>
         </is>
       </c>
       <c r="O476" t="inlineStr">
@@ -36715,7 +36715,7 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第六章 学习法治思想 提升法治素养</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -36765,7 +36765,7 @@
       </c>
       <c r="N477" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4006</t>
         </is>
       </c>
       <c r="O477" t="inlineStr">
@@ -36792,7 +36792,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第7章 社会主义现代化建设的教育,科技,人才战略</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -36842,7 +36842,7 @@
       </c>
       <c r="N478" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2108</t>
         </is>
       </c>
       <c r="O478" t="inlineStr">
@@ -36869,7 +36869,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第7章 社会主义现代化建设的教育,科技,人才战略</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="N479" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2108</t>
         </is>
       </c>
       <c r="O479" t="inlineStr">
@@ -36946,7 +36946,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="N480" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O480" t="inlineStr">
@@ -37023,7 +37023,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -37073,7 +37073,7 @@
       </c>
       <c r="N481" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O481" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -37150,7 +37150,7 @@
       </c>
       <c r="N482" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O482" t="inlineStr">
@@ -37177,7 +37177,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题五：资本主义论（上）</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -37227,7 +37227,7 @@
       </c>
       <c r="N483" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1006</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -37254,7 +37254,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题二：辩证唯物主义世界观</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -37304,7 +37304,7 @@
       </c>
       <c r="N484" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -37381,7 +37381,7 @@
       </c>
       <c r="N485" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -37485,7 +37485,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -37535,7 +37535,7 @@
       </c>
       <c r="N487" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -37562,7 +37562,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第2章 以中国式现代化全面推进中华民族伟大复兴</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -37612,7 +37612,7 @@
       </c>
       <c r="N488" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -37639,7 +37639,7 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第6章 推动高质量发展</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -37689,7 +37689,7 @@
       </c>
       <c r="N489" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2107</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -37716,7 +37716,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第三章 辛亥革命与君主专制制度的终结</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="N490" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3004</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -37793,7 +37793,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题七：社会主义论</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -37843,7 +37843,7 @@
       </c>
       <c r="N491" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1008</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -37870,7 +37870,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第二章 新民主主义革命理论</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="N492" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -37947,7 +37947,7 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题一：马克思主义观</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -37997,7 +37997,7 @@
       </c>
       <c r="N493" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1002</t>
         </is>
       </c>
       <c r="O493" t="inlineStr">
@@ -38024,7 +38024,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">第一章 领悟人生真谛 把握人生方向</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="N494" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4001</t>
         </is>
       </c>
       <c r="O494" t="inlineStr">
@@ -38101,7 +38101,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">专题三：辩证唯物主义认识论</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -38151,7 +38151,7 @@
       </c>
       <c r="N495" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">1004</t>
         </is>
       </c>
       <c r="O495" t="inlineStr">
@@ -38228,7 +38228,7 @@
       </c>
       <c r="N496" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="O496" t="inlineStr">
